--- a/ShopEntry.xlsx
+++ b/ShopEntry.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9937"/>
+    <workbookView windowWidth="24000" windowHeight="10657"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$206</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="182">
   <si>
     <t>Item-Name</t>
   </si>
@@ -537,18 +537,58 @@
   </si>
   <si>
     <t>tatri</t>
+  </si>
+  <si>
+    <t>jhumka</t>
+  </si>
+  <si>
+    <t>jhumaka</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>shyam bhog</t>
+  </si>
+  <si>
+    <t>ghee</t>
+  </si>
+  <si>
+    <t>palm</t>
+  </si>
+  <si>
+    <t>posta dana</t>
+  </si>
+  <si>
+    <t>soyam</t>
+  </si>
+  <si>
+    <t>Biswa</t>
+  </si>
+  <si>
+    <t>kisaan</t>
+  </si>
+  <si>
+    <t>machise</t>
+  </si>
+  <si>
+    <t>303 bidi</t>
+  </si>
+  <si>
+    <t>bidi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="179" formatCode="0.000_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1187,7 +1227,7 @@
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1534,7 +1574,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K200"/>
+  <dimension ref="A1:K234"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.5132743362832" customWidth="1"/>
@@ -7813,19 +7853,19 @@
       <c r="A180" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="3">
         <v>4</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D180" s="4">
+      <c r="D180" s="3">
         <v>1</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F180" s="4">
+      <c r="F180" s="3">
         <v>1</v>
       </c>
       <c r="G180" s="3" t="s">
@@ -7834,7 +7874,7 @@
       <c r="H180" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="I180" s="4">
+      <c r="I180" s="3">
         <v>908</v>
       </c>
       <c r="J180" s="2">
@@ -8539,6 +8579,1127 @@
       </c>
       <c r="K200" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201" t="s">
+        <v>84</v>
+      </c>
+      <c r="B201">
+        <v>5</v>
+      </c>
+      <c r="C201" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="E201" t="s">
+        <v>39</v>
+      </c>
+      <c r="F201">
+        <v>2</v>
+      </c>
+      <c r="G201" t="s">
+        <v>26</v>
+      </c>
+      <c r="H201" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201">
+        <v>1680</v>
+      </c>
+      <c r="J201" s="2">
+        <v>46123</v>
+      </c>
+      <c r="K201" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="A202" t="s">
+        <v>169</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>21</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202" t="s">
+        <v>22</v>
+      </c>
+      <c r="H202" t="s">
+        <v>170</v>
+      </c>
+      <c r="I202">
+        <v>1010</v>
+      </c>
+      <c r="J202" s="2">
+        <v>46123</v>
+      </c>
+      <c r="K202" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="A203" t="s">
+        <v>171</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203" t="s">
+        <v>21</v>
+      </c>
+      <c r="D203">
+        <v>2</v>
+      </c>
+      <c r="E203" t="s">
+        <v>13</v>
+      </c>
+      <c r="F203">
+        <v>12</v>
+      </c>
+      <c r="G203" t="s">
+        <v>22</v>
+      </c>
+      <c r="H203" t="s">
+        <v>171</v>
+      </c>
+      <c r="I203">
+        <v>590</v>
+      </c>
+      <c r="J203" s="2">
+        <v>46123</v>
+      </c>
+      <c r="K203" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="A204" t="s">
+        <v>172</v>
+      </c>
+      <c r="B204" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="C204" t="s">
+        <v>12</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204" t="s">
+        <v>39</v>
+      </c>
+      <c r="F204">
+        <v>25</v>
+      </c>
+      <c r="G204" t="s">
+        <v>26</v>
+      </c>
+      <c r="H204" t="s">
+        <v>173</v>
+      </c>
+      <c r="I204">
+        <v>750</v>
+      </c>
+      <c r="J204" s="2">
+        <v>46123</v>
+      </c>
+      <c r="K204" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" t="s">
+        <v>172</v>
+      </c>
+      <c r="B205" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C205" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205" t="s">
+        <v>39</v>
+      </c>
+      <c r="F205">
+        <v>10</v>
+      </c>
+      <c r="G205" t="s">
+        <v>26</v>
+      </c>
+      <c r="H205" t="s">
+        <v>173</v>
+      </c>
+      <c r="I205">
+        <v>700</v>
+      </c>
+      <c r="J205" s="2">
+        <v>46123</v>
+      </c>
+      <c r="K205" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" t="s">
+        <v>172</v>
+      </c>
+      <c r="B206" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C206" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206" t="s">
+        <v>39</v>
+      </c>
+      <c r="F206">
+        <v>50</v>
+      </c>
+      <c r="G206" t="s">
+        <v>26</v>
+      </c>
+      <c r="H206" t="s">
+        <v>173</v>
+      </c>
+      <c r="I206">
+        <v>800</v>
+      </c>
+      <c r="J206" s="2">
+        <v>46123</v>
+      </c>
+      <c r="K206" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="A207" t="s">
+        <v>174</v>
+      </c>
+      <c r="B207">
+        <v>15</v>
+      </c>
+      <c r="C207" t="s">
+        <v>12</v>
+      </c>
+      <c r="D207">
+        <v>5</v>
+      </c>
+      <c r="E207" t="s">
+        <v>25</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" t="s">
+        <v>26</v>
+      </c>
+      <c r="H207" t="s">
+        <v>29</v>
+      </c>
+      <c r="I207">
+        <v>12100</v>
+      </c>
+      <c r="J207" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K207" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" t="s">
+        <v>113</v>
+      </c>
+      <c r="B208">
+        <v>15</v>
+      </c>
+      <c r="C208" t="s">
+        <v>12</v>
+      </c>
+      <c r="D208">
+        <v>5</v>
+      </c>
+      <c r="E208" t="s">
+        <v>25</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208" t="s">
+        <v>26</v>
+      </c>
+      <c r="H208" t="s">
+        <v>29</v>
+      </c>
+      <c r="I208">
+        <v>12450</v>
+      </c>
+      <c r="J208" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K208" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11">
+      <c r="A209" t="s">
+        <v>127</v>
+      </c>
+      <c r="B209">
+        <v>30</v>
+      </c>
+      <c r="C209" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209" t="s">
+        <v>31</v>
+      </c>
+      <c r="H209" t="s">
+        <v>128</v>
+      </c>
+      <c r="I209">
+        <v>3450</v>
+      </c>
+      <c r="J209" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K209" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" t="s">
+        <v>159</v>
+      </c>
+      <c r="B210">
+        <v>30</v>
+      </c>
+      <c r="C210" t="s">
+        <v>12</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210" t="s">
+        <v>13</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210" t="s">
+        <v>31</v>
+      </c>
+      <c r="H210" t="s">
+        <v>160</v>
+      </c>
+      <c r="I210">
+        <v>2270</v>
+      </c>
+      <c r="J210" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K210" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" t="s">
+        <v>38</v>
+      </c>
+      <c r="I211">
+        <v>820</v>
+      </c>
+      <c r="J211" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K211" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="A212" t="s">
+        <v>42</v>
+      </c>
+      <c r="I212">
+        <v>820</v>
+      </c>
+      <c r="J212" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K212" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" t="s">
+        <v>43</v>
+      </c>
+      <c r="I213">
+        <v>640</v>
+      </c>
+      <c r="J213" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K213" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="A214" t="s">
+        <v>154</v>
+      </c>
+      <c r="B214">
+        <v>25</v>
+      </c>
+      <c r="C214" t="s">
+        <v>12</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214" t="s">
+        <v>51</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214" t="s">
+        <v>80</v>
+      </c>
+      <c r="H214" t="s">
+        <v>154</v>
+      </c>
+      <c r="I214">
+        <v>3500</v>
+      </c>
+      <c r="J214" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K214" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="A215" t="s">
+        <v>175</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215" t="s">
+        <v>12</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+      <c r="E215" t="s">
+        <v>21</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215" t="s">
+        <v>119</v>
+      </c>
+      <c r="H215" t="s">
+        <v>175</v>
+      </c>
+      <c r="I215">
+        <v>1300</v>
+      </c>
+      <c r="J215" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K215" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="A216" t="s">
+        <v>176</v>
+      </c>
+      <c r="B216">
+        <v>15</v>
+      </c>
+      <c r="C216" t="s">
+        <v>12</v>
+      </c>
+      <c r="D216">
+        <v>10</v>
+      </c>
+      <c r="E216" t="s">
+        <v>25</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216" t="s">
+        <v>26</v>
+      </c>
+      <c r="H216" t="s">
+        <v>29</v>
+      </c>
+      <c r="I216">
+        <v>23200</v>
+      </c>
+      <c r="J216" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K216" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="A217" t="s">
+        <v>28</v>
+      </c>
+      <c r="B217">
+        <v>15</v>
+      </c>
+      <c r="C217" t="s">
+        <v>12</v>
+      </c>
+      <c r="D217">
+        <v>10</v>
+      </c>
+      <c r="E217" t="s">
+        <v>25</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" t="s">
+        <v>26</v>
+      </c>
+      <c r="H217" t="s">
+        <v>29</v>
+      </c>
+      <c r="I217">
+        <v>24400</v>
+      </c>
+      <c r="J217" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K217" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11">
+      <c r="A218" t="s">
+        <v>113</v>
+      </c>
+      <c r="B218">
+        <v>10</v>
+      </c>
+      <c r="C218" t="s">
+        <v>12</v>
+      </c>
+      <c r="D218">
+        <v>10</v>
+      </c>
+      <c r="E218" t="s">
+        <v>39</v>
+      </c>
+      <c r="F218">
+        <v>10</v>
+      </c>
+      <c r="G218" t="s">
+        <v>26</v>
+      </c>
+      <c r="H218" t="s">
+        <v>29</v>
+      </c>
+      <c r="I218">
+        <v>10100</v>
+      </c>
+      <c r="J218" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K218" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="A219" t="s">
+        <v>19</v>
+      </c>
+      <c r="B219">
+        <v>50</v>
+      </c>
+      <c r="C219" t="s">
+        <v>12</v>
+      </c>
+      <c r="D219">
+        <v>4</v>
+      </c>
+      <c r="E219" t="s">
+        <v>13</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219" t="s">
+        <v>18</v>
+      </c>
+      <c r="I219">
+        <v>8660</v>
+      </c>
+      <c r="J219" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K219" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11">
+      <c r="A220" t="s">
+        <v>19</v>
+      </c>
+      <c r="B220">
+        <v>50</v>
+      </c>
+      <c r="C220" t="s">
+        <v>12</v>
+      </c>
+      <c r="D220">
+        <v>4</v>
+      </c>
+      <c r="E220" t="s">
+        <v>13</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220" t="s">
+        <v>18</v>
+      </c>
+      <c r="H220" t="s">
+        <v>177</v>
+      </c>
+      <c r="I220">
+        <v>8860</v>
+      </c>
+      <c r="J220" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K220" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="A221" t="s">
+        <v>107</v>
+      </c>
+      <c r="B221">
+        <v>30</v>
+      </c>
+      <c r="C221" t="s">
+        <v>12</v>
+      </c>
+      <c r="D221">
+        <v>2</v>
+      </c>
+      <c r="E221" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221" t="s">
+        <v>31</v>
+      </c>
+      <c r="H221" t="s">
+        <v>107</v>
+      </c>
+      <c r="I221">
+        <v>2970</v>
+      </c>
+      <c r="J221" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K221" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="A222" t="s">
+        <v>95</v>
+      </c>
+      <c r="B222">
+        <v>30</v>
+      </c>
+      <c r="C222" t="s">
+        <v>12</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222" t="s">
+        <v>13</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222" t="s">
+        <v>31</v>
+      </c>
+      <c r="H222" t="s">
+        <v>32</v>
+      </c>
+      <c r="I222">
+        <v>2040</v>
+      </c>
+      <c r="J222" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K222" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="A223" t="s">
+        <v>30</v>
+      </c>
+      <c r="B223">
+        <v>30</v>
+      </c>
+      <c r="C223" t="s">
+        <v>12</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223" t="s">
+        <v>13</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223" t="s">
+        <v>31</v>
+      </c>
+      <c r="H223" t="s">
+        <v>32</v>
+      </c>
+      <c r="I223">
+        <v>2040</v>
+      </c>
+      <c r="J223" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K223" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" t="s">
+        <v>93</v>
+      </c>
+      <c r="B224">
+        <v>30</v>
+      </c>
+      <c r="C224" t="s">
+        <v>12</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+      <c r="E224" t="s">
+        <v>13</v>
+      </c>
+      <c r="F224">
+        <v>1</v>
+      </c>
+      <c r="G224" t="s">
+        <v>31</v>
+      </c>
+      <c r="H224" t="s">
+        <v>93</v>
+      </c>
+      <c r="I224">
+        <v>2160</v>
+      </c>
+      <c r="J224" s="2">
+        <v>46118</v>
+      </c>
+      <c r="K224" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11">
+      <c r="A225" t="s">
+        <v>19</v>
+      </c>
+      <c r="B225">
+        <v>50</v>
+      </c>
+      <c r="C225" t="s">
+        <v>12</v>
+      </c>
+      <c r="D225">
+        <v>1</v>
+      </c>
+      <c r="E225" t="s">
+        <v>13</v>
+      </c>
+      <c r="F225">
+        <v>4</v>
+      </c>
+      <c r="G225" t="s">
+        <v>18</v>
+      </c>
+      <c r="I225">
+        <v>8660</v>
+      </c>
+      <c r="J225" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K225" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11">
+      <c r="A226" t="s">
+        <v>132</v>
+      </c>
+      <c r="B226">
+        <v>5</v>
+      </c>
+      <c r="C226" t="s">
+        <v>12</v>
+      </c>
+      <c r="D226">
+        <v>2</v>
+      </c>
+      <c r="E226" t="s">
+        <v>13</v>
+      </c>
+      <c r="F226">
+        <v>5</v>
+      </c>
+      <c r="G226" t="s">
+        <v>133</v>
+      </c>
+      <c r="H226" t="s">
+        <v>133</v>
+      </c>
+      <c r="I226">
+        <v>2710</v>
+      </c>
+      <c r="J226" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K226" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11">
+      <c r="A227" t="s">
+        <v>98</v>
+      </c>
+      <c r="B227">
+        <v>30</v>
+      </c>
+      <c r="C227" t="s">
+        <v>12</v>
+      </c>
+      <c r="D227">
+        <v>1</v>
+      </c>
+      <c r="E227" t="s">
+        <v>13</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227" t="s">
+        <v>31</v>
+      </c>
+      <c r="H227" t="s">
+        <v>99</v>
+      </c>
+      <c r="I227">
+        <v>3330</v>
+      </c>
+      <c r="J227" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K227" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="A228" t="s">
+        <v>90</v>
+      </c>
+      <c r="B228">
+        <v>30</v>
+      </c>
+      <c r="C228" t="s">
+        <v>12</v>
+      </c>
+      <c r="D228">
+        <v>2</v>
+      </c>
+      <c r="E228" t="s">
+        <v>13</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228" t="s">
+        <v>31</v>
+      </c>
+      <c r="H228" t="s">
+        <v>87</v>
+      </c>
+      <c r="I228">
+        <v>6660</v>
+      </c>
+      <c r="J228" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K228" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="A229" t="s">
+        <v>178</v>
+      </c>
+      <c r="B229">
+        <v>1</v>
+      </c>
+      <c r="C229" t="s">
+        <v>47</v>
+      </c>
+      <c r="D229">
+        <v>5</v>
+      </c>
+      <c r="E229" t="s">
+        <v>47</v>
+      </c>
+      <c r="F229">
+        <v>5</v>
+      </c>
+      <c r="G229" t="s">
+        <v>48</v>
+      </c>
+      <c r="H229" t="s">
+        <v>179</v>
+      </c>
+      <c r="I229">
+        <v>2300</v>
+      </c>
+      <c r="J229" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K229" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="A230" t="s">
+        <v>180</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230" t="s">
+        <v>47</v>
+      </c>
+      <c r="D230">
+        <v>5</v>
+      </c>
+      <c r="E230" t="s">
+        <v>47</v>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="G230" t="s">
+        <v>22</v>
+      </c>
+      <c r="H230" t="s">
+        <v>181</v>
+      </c>
+      <c r="I230">
+        <v>730</v>
+      </c>
+      <c r="J230" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K230" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="A231" t="s">
+        <v>135</v>
+      </c>
+      <c r="B231">
+        <v>25</v>
+      </c>
+      <c r="C231" t="s">
+        <v>12</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231" t="s">
+        <v>51</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="G231" t="s">
+        <v>80</v>
+      </c>
+      <c r="H231" t="s">
+        <v>135</v>
+      </c>
+      <c r="I231">
+        <v>8625</v>
+      </c>
+      <c r="J231" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K231" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="A232" t="s">
+        <v>134</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232" t="s">
+        <v>12</v>
+      </c>
+      <c r="D232">
+        <v>10</v>
+      </c>
+      <c r="E232" t="s">
+        <v>21</v>
+      </c>
+      <c r="F232">
+        <v>1</v>
+      </c>
+      <c r="G232" t="s">
+        <v>80</v>
+      </c>
+      <c r="H232" t="s">
+        <v>135</v>
+      </c>
+      <c r="I232">
+        <v>2800</v>
+      </c>
+      <c r="J232" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K232" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" t="s">
+        <v>112</v>
+      </c>
+      <c r="B233">
+        <v>50</v>
+      </c>
+      <c r="C233" t="s">
+        <v>12</v>
+      </c>
+      <c r="D233">
+        <v>2</v>
+      </c>
+      <c r="E233" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233" t="s">
+        <v>34</v>
+      </c>
+      <c r="H233" t="s">
+        <v>112</v>
+      </c>
+      <c r="I233">
+        <v>2800</v>
+      </c>
+      <c r="J233" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K233" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="A234" t="s">
+        <v>33</v>
+      </c>
+      <c r="B234">
+        <v>26</v>
+      </c>
+      <c r="C234" t="s">
+        <v>12</v>
+      </c>
+      <c r="D234">
+        <v>4</v>
+      </c>
+      <c r="E234" t="s">
+        <v>13</v>
+      </c>
+      <c r="F234">
+        <v>1</v>
+      </c>
+      <c r="G234" t="s">
+        <v>34</v>
+      </c>
+      <c r="H234" t="s">
+        <v>33</v>
+      </c>
+      <c r="I234">
+        <v>2960</v>
+      </c>
+      <c r="J234" s="2">
+        <v>46116</v>
+      </c>
+      <c r="K234" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
